--- a/artfynd/A 29379-2023 artfynd.xlsx
+++ b/artfynd/A 29379-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29379-2023 artfynd.xlsx
+++ b/artfynd/A 29379-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85641448</v>
+        <v>85641581</v>
       </c>
       <c r="B2" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332391.228313624</v>
+        <v>332391</v>
       </c>
       <c r="R2" t="n">
-        <v>6609616.809549077</v>
+        <v>6609617</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -756,27 +747,18 @@
           <t>2020-01-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-01-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>85641471</v>
+        <v>85641488</v>
       </c>
       <c r="B3" t="n">
-        <v>73507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332391.228313624</v>
+        <v>332391</v>
       </c>
       <c r="R3" t="n">
-        <v>6609616.809549077</v>
+        <v>6609617</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -871,19 +848,9 @@
           <t>2020-01-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-01-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85641488</v>
+        <v>85641522</v>
       </c>
       <c r="B4" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332391.228313624</v>
+        <v>332391</v>
       </c>
       <c r="R4" t="n">
-        <v>6609616.809549077</v>
+        <v>6609617</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -987,19 +949,9 @@
           <t>2020-01-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-01-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,43 +979,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>85641581</v>
+        <v>85641471</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1071,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>332391.228313624</v>
+        <v>332391</v>
       </c>
       <c r="R5" t="n">
-        <v>6609616.809549077</v>
+        <v>6609617</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1104,19 +1050,9 @@
           <t>2020-01-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-01-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,12 +1083,7 @@
         <v>85641481</v>
       </c>
       <c r="B6" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>332391.228313624</v>
+        <v>332391</v>
       </c>
       <c r="R6" t="n">
-        <v>6609616.809549077</v>
+        <v>6609617</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1220,19 +1151,9 @@
           <t>2020-01-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-01-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>85641522</v>
+        <v>85641448</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,26 +1192,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>332391.228313624</v>
+        <v>332391</v>
       </c>
       <c r="R7" t="n">
-        <v>6609616.809549077</v>
+        <v>6609617</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1336,28 +1257,17 @@
           <t>2020-01-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-01-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
